--- a/out/LSTM_Base_repeat_4_000007.xlsx
+++ b/out/LSTM_Base_repeat_4_000007.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.103979445500941</v>
+        <v>8.62785843586423</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.103979445500941</v>
+        <v>8.62785843586423</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.103979445500941</v>
+        <v>9.227858435864231</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA5" t="n">
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-1.103979445500941</v>
+        <v>0.0804624974787484</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.103979445500941</v>
+        <v>0.0804624974787484</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>2.737873157325433</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>2.737873157325433</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>2.737873157325433</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.5039794455009408</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>2.737873157325433</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>2.737873157325433</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>2.737873157325433</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>2.737873157325433</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>2.737873157325433</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>2.737873157325433</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>2.737873157325433</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>2.737873157325433</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>2.137873157325433</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>2.137873157325433</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>2.737873157325433</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>2.737873157325433</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>2.137873157325433</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>2.137873157325433</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>2.737873157325433</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>2.737873157325433</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>2.737873157325433</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,13 +31946,13 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>2.737873157325433</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC39" t="n">
-        <v>-0.0003087850468152901</v>
+        <v>-6.038105188275221e-05</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>3.55983554350491</v>
+        <v>0.6961042754547568</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32741,13 +32741,13 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>2.737873157325433</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC40" t="n">
-        <v>7.12517395032102</v>
+        <v>1.393284754049746</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.5338132193761543</v>
+        <v>0.1043839412694196</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33539,10 +33539,10 @@
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC41" t="n">
-        <v>4.628187056613684</v>
+        <v>0.9050139873536248</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.6674402158090327</v>
+        <v>0.1305139476654237</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34334,10 +34334,10 @@
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC42" t="n">
-        <v>5.429339042117581</v>
+        <v>1.061674472939382</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.9567722214177415</v>
+        <v>0.1870911250288232</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35126,13 +35126,13 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>2.137873157325433</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC43" t="n">
-        <v>6.675820260803341</v>
+        <v>1.305416430128927</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>1.023557107740903</v>
+        <v>0.2001504448110093</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>2.137873157325433</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC44" t="n">
-        <v>7.766233264758825</v>
+        <v>1.518640143900103</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>1.084763488968523</v>
+        <v>0.2121183915624241</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>2.737873157325433</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC45" t="n">
-        <v>8.91228206412217</v>
+        <v>1.742743104207468</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.4895342531624715</v>
+        <v>0.09572575083263495</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>2.737873157325433</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC46" t="n">
-        <v>8.805684170609595</v>
+        <v>1.721898468050247</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.2364226693599036</v>
+        <v>0.04623051919669491</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC47" t="n">
-        <v>8.788611394420764</v>
+        <v>1.71855998084306</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.1126477503035147</v>
+        <v>0.02202746602705347</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC48" t="n">
-        <v>8.777297700012841</v>
+        <v>1.716347619634103</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.0333767426441922</v>
+        <v>0.006523580880987169</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC49" t="n">
-        <v>8.731282943705352</v>
+        <v>1.707346355452162</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.02207795110083229</v>
+        <v>0.004313887701662389</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC50" t="n">
-        <v>8.742043949127989</v>
+        <v>1.709447096823808</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.01129769243397631</v>
+        <v>0.002204963193759101</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC51" t="n">
-        <v>8.742547509030059</v>
+        <v>1.709541551479308</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.005777267317571653</v>
+        <v>0.001125481580367856</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC52" t="n">
-        <v>8.742796643046288</v>
+        <v>1.709586259537464</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.002168773482149537</v>
+        <v>0.0004203693234568383</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC53" t="n">
-        <v>8.741352542008661</v>
+        <v>1.70929965271882</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.001179708583343353</v>
+        <v>0.0002268266796096673</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC54" t="n">
-        <v>8.741541974744717</v>
+        <v>1.709332699793215</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0005656161045008799</v>
+        <v>0.000106262193078166</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC55" t="n">
-        <v>8.741492749251726</v>
+        <v>1.709319046125635</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.0003482398871591795</v>
+        <v>6.387685822045283e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC56" t="n">
-        <v>8.741623346095524</v>
+        <v>1.70934067507415</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.0001792570791898958</v>
+        <v>3.10279205119908e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC57" t="n">
-        <v>8.741634445126937</v>
+        <v>1.709338859507548</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>8.4918381770666e-05</v>
+        <v>1.29836763541332e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>2.737873157325433</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC58" t="n">
-        <v>8.741623879443726</v>
+        <v>1.709332746370905</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>5.256158699932203e-05</v>
+        <v>6.512317399864405e-06</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>2.737873157325433</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC59" t="n">
-        <v>8.741644044651533</v>
+        <v>1.709332779412467</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>2.064344810800705e-05</v>
+        <v>-3.375548894532629e-07</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.5039794455009408</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC60" t="n">
-        <v>8.741633898277733</v>
+        <v>1.70932675070418</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>6.323060732339969e-06</v>
+        <v>-2.941261685029097e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.5039794455009408</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC61" t="n">
-        <v>8.741625747166712</v>
+        <v>1.709321066170152</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>1.675769385467227e-06</v>
+        <v>-3.887371769088796e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC62" t="n">
-        <v>8.7416217393608</v>
+        <v>1.709316314894938</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>-2.093548687745288e-06</v>
+        <v>-4.031182895915095e-06</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC63" t="n">
-        <v>8.741615871918116</v>
+        <v>1.709311025747376</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>-4.053889915940302e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC64" t="n">
-        <v>8.741610802562747</v>
+        <v>1.709311003013075</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>-3.735991635587426e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>2.737873157325433</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC65" t="n">
-        <v>8.741606437588779</v>
+        <v>1.709311321293292</v>
       </c>
     </row>
     <row r="66">
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>2.737873157325433</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC66" t="n">
-        <v>8.741607528835235</v>
+        <v>1.709312412539749</v>
       </c>
     </row>
     <row r="67">
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>2.737873157325433</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC67" t="n">
-        <v>8.741606839228099</v>
+        <v>1.709311722932613</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.5039794455009408</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC68" t="n">
-        <v>8.741606869540501</v>
+        <v>1.709311753245014</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.5039794455009408</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC69" t="n">
-        <v>8.74160668008799</v>
+        <v>1.709311563792504</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC70" t="n">
-        <v>8.741606733134695</v>
+        <v>1.709311616839207</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC71" t="n">
-        <v>8.741606786181396</v>
+        <v>1.70931166988591</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC72" t="n">
-        <v>8.741606748290895</v>
+        <v>1.709311631995408</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC73" t="n">
-        <v>8.741606619463189</v>
+        <v>1.709311503167702</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC74" t="n">
-        <v>8.74160647547928</v>
+        <v>1.709311359183794</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC75" t="n">
-        <v>8.741606316339173</v>
+        <v>1.709311200043685</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC76" t="n">
-        <v>8.741606369385876</v>
+        <v>1.709311253090388</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC77" t="n">
-        <v>8.741606316339173</v>
+        <v>1.709311200043685</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC78" t="n">
-        <v>8.741606316339173</v>
+        <v>1.709311200043685</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC79" t="n">
-        <v>8.741606134464764</v>
+        <v>1.709311018169276</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC80" t="n">
-        <v>8.741606301182973</v>
+        <v>1.709311184887485</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC81" t="n">
-        <v>8.741606498213581</v>
+        <v>1.709311381918095</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC82" t="n">
-        <v>8.741606339073474</v>
+        <v>1.709311222777987</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC83" t="n">
-        <v>8.741606376963976</v>
+        <v>1.709311260668489</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC84" t="n">
-        <v>8.741606573994586</v>
+        <v>1.709311457699099</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC85" t="n">
-        <v>8.741606551260285</v>
+        <v>1.709311434964798</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC86" t="n">
-        <v>8.741606399698275</v>
+        <v>1.70931128340279</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC87" t="n">
-        <v>8.741606323917273</v>
+        <v>1.709311207621786</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC88" t="n">
-        <v>8.741606422432577</v>
+        <v>1.709311306137091</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC89" t="n">
-        <v>8.741606430010679</v>
+        <v>1.709311313715192</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC90" t="n">
-        <v>8.741606695244192</v>
+        <v>1.709311578948705</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC91" t="n">
-        <v>8.741606399698275</v>
+        <v>1.70931128340279</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC92" t="n">
-        <v>8.741606642197489</v>
+        <v>1.709311525902003</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC93" t="n">
-        <v>8.741606725556593</v>
+        <v>1.709311609261107</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC94" t="n">
-        <v>8.741606558838384</v>
+        <v>1.709311442542898</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC95" t="n">
-        <v>8.741606748290895</v>
+        <v>1.709311631995408</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC96" t="n">
-        <v>8.741606399698275</v>
+        <v>1.70931128340279</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC97" t="n">
-        <v>8.741606195089565</v>
+        <v>1.709311078794079</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC98" t="n">
-        <v>8.741606308761071</v>
+        <v>1.709311192465585</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC99" t="n">
-        <v>8.741606323917273</v>
+        <v>1.709311207621786</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC100" t="n">
-        <v>8.741606088996161</v>
+        <v>1.709310972700674</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC101" t="n">
-        <v>8.741606149620964</v>
+        <v>1.709311033325477</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC102" t="n">
-        <v>8.741606020793258</v>
+        <v>1.70931090449777</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC103" t="n">
-        <v>8.741606157199064</v>
+        <v>1.709311040903577</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC104" t="n">
-        <v>8.741606331495372</v>
+        <v>1.709311215199886</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC105" t="n">
-        <v>8.74160647547928</v>
+        <v>1.709311359183794</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC106" t="n">
-        <v>8.741606308761071</v>
+        <v>1.709311192465585</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC107" t="n">
-        <v>8.741606301182973</v>
+        <v>1.709311184887485</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC108" t="n">
-        <v>8.741606013215156</v>
+        <v>1.70931089691967</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC109" t="n">
-        <v>8.741606028371356</v>
+        <v>1.709310912075871</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC110" t="n">
-        <v>8.74160625571437</v>
+        <v>1.709311139418882</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC111" t="n">
-        <v>8.741606240558168</v>
+        <v>1.709311124262682</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC112" t="n">
-        <v>8.741606346651574</v>
+        <v>1.709311230356087</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC113" t="n">
-        <v>8.741606073839959</v>
+        <v>1.709310957544473</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC114" t="n">
-        <v>8.741606172355265</v>
+        <v>1.709311056059778</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC115" t="n">
-        <v>8.741606323917273</v>
+        <v>1.709311207621786</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC116" t="n">
-        <v>8.741606339073474</v>
+        <v>1.709311222777987</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC117" t="n">
-        <v>8.741606316339173</v>
+        <v>1.709311200043685</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC118" t="n">
-        <v>8.741606399698275</v>
+        <v>1.70931128340279</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC119" t="n">
-        <v>8.741606498213581</v>
+        <v>1.709311381918095</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC120" t="n">
-        <v>8.741606331495372</v>
+        <v>1.709311215199886</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC121" t="n">
-        <v>8.741606316339173</v>
+        <v>1.709311200043685</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC122" t="n">
-        <v>8.741606286026769</v>
+        <v>1.709311169731284</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC123" t="n">
-        <v>8.74160627087057</v>
+        <v>1.709311154575083</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC124" t="n">
-        <v>8.741606308761071</v>
+        <v>1.709311192465585</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC125" t="n">
-        <v>8.741606323917273</v>
+        <v>1.709311207621786</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC126" t="n">
-        <v>8.741606316339173</v>
+        <v>1.709311200043685</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM_Base_repeat_4_000007.xlsx
+++ b/out/LSTM_Base_repeat_4_000007.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.103979445500941</v>
+        <v>0.3496946894453832</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>2.737873157325433</v>
+        <v>1.090689570091412</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>2.737873157325433</v>
+        <v>1.83168445073744</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>2.737873157325433</v>
+        <v>1.090689570091412</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.5039794455009408</v>
+        <v>1.090689570091412</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>2.737873157325433</v>
+        <v>0.3496946894453832</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.103979445500941</v>
+        <v>1.090689570091412</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>2.737873157325433</v>
+        <v>1.090689570091412</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>2.737873157325433</v>
+        <v>1.83168445073744</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>2.737873157325433</v>
+        <v>1.83168445073744</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>2.737873157325433</v>
+        <v>1.83168445073744</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>1</v>
       </c>
       <c r="JB24" t="n">
-        <v>2.737873157325433</v>
+        <v>1.83168445073744</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>2.737873157325433</v>
+        <v>1.83168445073744</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>1</v>
       </c>
       <c r="JB26" t="n">
-        <v>2.737873157325433</v>
+        <v>1.090689570091412</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-1.103979445500941</v>
+        <v>0.1496946894453832</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-1.103979445500941</v>
+        <v>0.1496946894453832</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>2.137873157325433</v>
+        <v>0.8906895700914115</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>2.137873157325433</v>
+        <v>1.63168445073744</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>2.737873157325433</v>
+        <v>1.83168445073744</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>2.737873157325433</v>
+        <v>1.090689570091412</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.103979445500941</v>
+        <v>1.090689570091412</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>2.137873157325433</v>
+        <v>0.8906895700914115</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>2.137873157325433</v>
+        <v>1.83168445073744</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>2.737873157325433</v>
+        <v>1.83168445073744</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>2.737873157325433</v>
+        <v>1.83168445073744</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>2.737873157325433</v>
+        <v>1.83168445073744</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,10 +31949,10 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>2.737873157325433</v>
+        <v>1.83168445073744</v>
       </c>
       <c r="JC39" t="n">
-        <v>-0.0003087850468152901</v>
+        <v>-0.0002396808027515653</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>3.55983554350491</v>
+        <v>2.763165669875081</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32744,10 +32744,10 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>2.737873157325433</v>
+        <v>1.090689570091412</v>
       </c>
       <c r="JC40" t="n">
-        <v>7.12517395032102</v>
+        <v>5.530602695210746</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.5338132193761543</v>
+        <v>0.4143489953694587</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33539,10 +33539,10 @@
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-1.103979445500941</v>
+        <v>0.1496946894453832</v>
       </c>
       <c r="JC41" t="n">
-        <v>4.628187056613684</v>
+        <v>3.592426513096849</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.6674402158090327</v>
+        <v>0.5180711213966482</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34334,10 +34334,10 @@
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-1.103979445500941</v>
+        <v>0.1496946894453832</v>
       </c>
       <c r="JC42" t="n">
-        <v>5.429339042117581</v>
+        <v>4.214285516657267</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.9567722214177415</v>
+        <v>0.7426523329458294</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35129,10 +35129,10 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>2.137873157325433</v>
+        <v>0.8906895700914117</v>
       </c>
       <c r="JC43" t="n">
-        <v>6.675820260803341</v>
+        <v>5.181811757220412</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>1.023557107740903</v>
+        <v>0.7944912398974422</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>2.137873157325433</v>
+        <v>1.63168445073744</v>
       </c>
       <c r="JC44" t="n">
-        <v>7.766233264758825</v>
+        <v>6.028196949566889</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>1.084763488968523</v>
+        <v>0.8420005771651439</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>2.737873157325433</v>
+        <v>1.83168445073744</v>
       </c>
       <c r="JC45" t="n">
-        <v>8.91228206412217</v>
+        <v>6.917766983143647</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.4895342531624715</v>
+        <v>0.3799785344329387</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>2.737873157325433</v>
+        <v>1.090689570091412</v>
       </c>
       <c r="JC46" t="n">
-        <v>8.805684170609595</v>
+        <v>6.835025108445538</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.2364226693599036</v>
+        <v>0.1835122646265243</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-1.103979445500941</v>
+        <v>0.1496946894453832</v>
       </c>
       <c r="JC47" t="n">
-        <v>8.788611394420764</v>
+        <v>6.821773102704443</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.1126477503035147</v>
+        <v>0.08743813058663204</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC48" t="n">
-        <v>8.777297700012841</v>
+        <v>6.812991304446424</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.0333767426441922</v>
+        <v>0.02590730817096692</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC49" t="n">
-        <v>8.731282943705352</v>
+        <v>6.777274151917468</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.02207795110083229</v>
+        <v>0.01713671825815635</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC50" t="n">
-        <v>8.742043949127989</v>
+        <v>6.785626987913744</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.01129769243397631</v>
+        <v>0.008768927782168255</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC51" t="n">
-        <v>8.742547509030059</v>
+        <v>6.786016749463758</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.005777267317571653</v>
+        <v>0.004482699808797777</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC52" t="n">
-        <v>8.742796643046288</v>
+        <v>6.786209009218313</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.002168773482149537</v>
+        <v>0.001682096480400876</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC53" t="n">
-        <v>8.741352542008661</v>
+        <v>6.785086852381644</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.001179708583343353</v>
+        <v>0.0009148816646433416</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC54" t="n">
-        <v>8.741541974744717</v>
+        <v>6.785232822089654</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0005656161045008799</v>
+        <v>0.000437664582460989</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC55" t="n">
-        <v>8.741492749251726</v>
+        <v>6.785193483142717</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.0003482398871591795</v>
+        <v>0.0002695234777643763</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC56" t="n">
-        <v>8.741623346095524</v>
+        <v>6.785293863419652</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.0001792570791898958</v>
+        <v>0.0001380823128904778</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.103979445500941</v>
+        <v>0.3496946894453832</v>
       </c>
       <c r="JC57" t="n">
-        <v>8.741634445126937</v>
+        <v>6.785301375062728</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>8.4918381770666e-05</v>
+        <v>6.493651915496244e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>2.737873157325433</v>
+        <v>1.090689570091412</v>
       </c>
       <c r="JC58" t="n">
-        <v>8.741623879443726</v>
+        <v>6.785292046198006</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>5.256158699932203e-05</v>
+        <v>3.97701232216949e-05</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>2.737873157325433</v>
+        <v>1.090689570091412</v>
       </c>
       <c r="JC59" t="n">
-        <v>8.741644044651533</v>
+        <v>6.785306619137414</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>2.064344810800705e-05</v>
+        <v>1.481539171982363e-05</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.5039794455009408</v>
+        <v>0.3496946894453833</v>
       </c>
       <c r="JC60" t="n">
-        <v>8.741633898277733</v>
+        <v>6.78529761655959</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>6.323060732339969e-06</v>
+        <v>4.264322417369065e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.5039794455009408</v>
+        <v>-0.3913001912006451</v>
       </c>
       <c r="JC61" t="n">
-        <v>8.741625747166712</v>
+        <v>6.785290149982596</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>1.675769385467227e-06</v>
+        <v>-5.494870763551826e-07</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC62" t="n">
-        <v>8.7416217393608</v>
+        <v>6.785285894804425</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>-2.093548687745288e-06</v>
+        <v>-3.062365791830193e-06</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC63" t="n">
-        <v>8.741615871918116</v>
+        <v>6.785280172525395</v>
       </c>
     </row>
     <row r="64">
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.103979445500941</v>
+        <v>0.1496946894453832</v>
       </c>
       <c r="JC64" t="n">
-        <v>8.741610802562747</v>
+        <v>6.785275103170026</v>
       </c>
     </row>
     <row r="65">
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>2.737873157325433</v>
+        <v>1.090689570091412</v>
       </c>
       <c r="JC65" t="n">
-        <v>8.741606437588779</v>
+        <v>6.785270738196057</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>2.737873157325433</v>
+        <v>1.83168445073744</v>
       </c>
       <c r="JC66" t="n">
-        <v>8.741607528835235</v>
+        <v>6.785271829442515</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>2.737873157325433</v>
+        <v>1.090689570091412</v>
       </c>
       <c r="JC67" t="n">
-        <v>8.741606839228099</v>
+        <v>6.785271139835378</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.5039794455009408</v>
+        <v>0.3496946894453833</v>
       </c>
       <c r="JC68" t="n">
-        <v>8.741606869540501</v>
+        <v>6.78527117014778</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.5039794455009408</v>
+        <v>-0.3913001912006451</v>
       </c>
       <c r="JC69" t="n">
-        <v>8.74160668008799</v>
+        <v>6.78527098069527</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC70" t="n">
-        <v>8.741606733134695</v>
+        <v>6.785271033741973</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC71" t="n">
-        <v>8.741606786181396</v>
+        <v>6.785271086788676</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC72" t="n">
-        <v>8.741606748290895</v>
+        <v>6.785271048898173</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC73" t="n">
-        <v>8.741606619463189</v>
+        <v>6.785270920070467</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC74" t="n">
-        <v>8.74160647547928</v>
+        <v>6.785270776086559</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC75" t="n">
-        <v>8.741606316339173</v>
+        <v>6.785270616946451</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC76" t="n">
-        <v>8.741606369385876</v>
+        <v>6.785270669993154</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC77" t="n">
-        <v>8.741606316339173</v>
+        <v>6.785270616946451</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC78" t="n">
-        <v>8.741606316339173</v>
+        <v>6.785270616946451</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC79" t="n">
-        <v>8.741606134464764</v>
+        <v>6.785270435072042</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC80" t="n">
-        <v>8.741606301182973</v>
+        <v>6.78527060179025</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC81" t="n">
-        <v>8.741606498213581</v>
+        <v>6.785270798820861</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC82" t="n">
-        <v>8.741606339073474</v>
+        <v>6.785270639680753</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC83" t="n">
-        <v>8.741606376963976</v>
+        <v>6.785270677571254</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC84" t="n">
-        <v>8.741606573994586</v>
+        <v>6.785270874601864</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC85" t="n">
-        <v>8.741606551260285</v>
+        <v>6.785270851867563</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC86" t="n">
-        <v>8.741606399698275</v>
+        <v>6.785270700305555</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC87" t="n">
-        <v>8.741606323917273</v>
+        <v>6.785270624524552</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC88" t="n">
-        <v>8.741606422432577</v>
+        <v>6.785270723039857</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC89" t="n">
-        <v>8.741606430010679</v>
+        <v>6.785270730617957</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC90" t="n">
-        <v>8.741606695244192</v>
+        <v>6.785270995851471</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC91" t="n">
-        <v>8.741606399698275</v>
+        <v>6.785270700305555</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC92" t="n">
-        <v>8.741606642197489</v>
+        <v>6.785270942804768</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC93" t="n">
-        <v>8.741606725556593</v>
+        <v>6.785271026163873</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC94" t="n">
-        <v>8.741606558838384</v>
+        <v>6.785270859445664</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC95" t="n">
-        <v>8.741606748290895</v>
+        <v>6.785271048898173</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC96" t="n">
-        <v>8.741606399698275</v>
+        <v>6.785270700305555</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC97" t="n">
-        <v>8.741606195089565</v>
+        <v>6.785270495696844</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC98" t="n">
-        <v>8.741606308761071</v>
+        <v>6.78527060936835</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC99" t="n">
-        <v>8.741606323917273</v>
+        <v>6.785270624524552</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC100" t="n">
-        <v>8.741606088996161</v>
+        <v>6.78527038960344</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC101" t="n">
-        <v>8.741606149620964</v>
+        <v>6.785270450228242</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC102" t="n">
-        <v>8.741606020793258</v>
+        <v>6.785270321400535</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC103" t="n">
-        <v>8.741606157199064</v>
+        <v>6.785270457806344</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC104" t="n">
-        <v>8.741606331495372</v>
+        <v>6.785270632102652</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC105" t="n">
-        <v>8.74160647547928</v>
+        <v>6.785270776086559</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC106" t="n">
-        <v>8.741606308761071</v>
+        <v>6.78527060936835</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC107" t="n">
-        <v>8.741606301182973</v>
+        <v>6.78527060179025</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC108" t="n">
-        <v>8.741606013215156</v>
+        <v>6.785270313822435</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC109" t="n">
-        <v>8.741606028371356</v>
+        <v>6.785270328978636</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC110" t="n">
-        <v>8.74160625571437</v>
+        <v>6.785270556321648</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC111" t="n">
-        <v>8.741606240558168</v>
+        <v>6.785270541165447</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC112" t="n">
-        <v>8.741606346651574</v>
+        <v>6.785270647258852</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC113" t="n">
-        <v>8.741606073839959</v>
+        <v>6.785270374447238</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC114" t="n">
-        <v>8.741606172355265</v>
+        <v>6.785270472962543</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC115" t="n">
-        <v>8.741606323917273</v>
+        <v>6.785270624524552</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC116" t="n">
-        <v>8.741606339073474</v>
+        <v>6.785270639680753</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC117" t="n">
-        <v>8.741606316339173</v>
+        <v>6.785270616946451</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC118" t="n">
-        <v>8.741606399698275</v>
+        <v>6.785270700305555</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC119" t="n">
-        <v>8.741606498213581</v>
+        <v>6.785270798820861</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC120" t="n">
-        <v>8.741606331495372</v>
+        <v>6.785270632102652</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC121" t="n">
-        <v>8.741606316339173</v>
+        <v>6.785270616946451</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC122" t="n">
-        <v>8.741606286026769</v>
+        <v>6.785270586634049</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC123" t="n">
-        <v>8.74160627087057</v>
+        <v>6.785270571477849</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC124" t="n">
-        <v>8.741606308761071</v>
+        <v>6.78527060936835</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC125" t="n">
-        <v>8.741606323917273</v>
+        <v>6.785270624524552</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.103979445500941</v>
+        <v>-0.5913001912006451</v>
       </c>
       <c r="JC126" t="n">
-        <v>8.741606316339173</v>
+        <v>6.785270616946451</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM_Base_repeat_4_000007.xlsx
+++ b/out/LSTM_Base_repeat_4_000007.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>-0.00973052904009819</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.5913001912006451</v>
+        <v>-1.28</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>-0.007014743983745575</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.5913001912006451</v>
+        <v>-0.8599999999999997</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>-0.004381240345537663</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.5913001912006451</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>-0.0001538116484880447</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.5913001912006451</v>
+        <v>-0.16</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>-0.0003320919349789619</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.5913001912006451</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>-0.001255561597645283</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.5913001912006451</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>-0.001947927288711071</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.5913001912006451</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>-0.001762302126735449</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.5913001912006451</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>-0.001169168390333652</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.5913001912006451</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>-0.0007159053348004818</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.5913001912006451</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>-0.0006384267471730709</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.5913001912006451</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>-0.0006412258371710777</v>
       </c>
       <c r="JB13" t="n">
-        <v>0.3496946894453832</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>9.525101631879807e-05</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.090689570091412</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0.000196253415197134</v>
       </c>
       <c r="JB15" t="n">
-        <v>1.83168445073744</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0.0004627611488103867</v>
       </c>
       <c r="JB16" t="n">
-        <v>1.090689570091412</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>-1.718662679195404e-05</v>
       </c>
       <c r="JB17" t="n">
-        <v>1.090689570091412</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>8.65105539560318e-06</v>
       </c>
       <c r="JB18" t="n">
-        <v>0.3496946894453832</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>-0.0001525371335446835</v>
       </c>
       <c r="JB19" t="n">
-        <v>1.090689570091412</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0.000282791443169117</v>
       </c>
       <c r="JB20" t="n">
-        <v>1.090689570091412</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0.0008824029937386513</v>
       </c>
       <c r="JB21" t="n">
-        <v>1.83168445073744</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0.001947448588907719</v>
       </c>
       <c r="JB22" t="n">
-        <v>1.83168445073744</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0.003741101361811161</v>
       </c>
       <c r="JB23" t="n">
-        <v>1.83168445073744</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0.002558748237788677</v>
       </c>
       <c r="JB24" t="n">
-        <v>1.83168445073744</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.001024768687784672</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.83168445073744</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>6.357580423355103e-05</v>
       </c>
       <c r="JB26" t="n">
-        <v>1.090689570091412</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>-0.0003764512948691845</v>
       </c>
       <c r="JB27" t="n">
-        <v>0.1496946894453832</v>
+        <v>-0.16</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0</v>
+        <v>-0.0006624455563724041</v>
       </c>
       <c r="JB28" t="n">
-        <v>0.1496946894453832</v>
+        <v>-0.16</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0.0006321342661976814</v>
       </c>
       <c r="JB29" t="n">
-        <v>0.8906895700914115</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0.001189104281365871</v>
       </c>
       <c r="JB30" t="n">
-        <v>1.63168445073744</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0.0007740408182144165</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.83168445073744</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0.0003787796013057232</v>
       </c>
       <c r="JB32" t="n">
-        <v>1.090689570091412</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>-9.118206799030304e-05</v>
       </c>
       <c r="JB33" t="n">
-        <v>1.090689570091412</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>6.627105176448822e-05</v>
       </c>
       <c r="JB34" t="n">
-        <v>0.8906895700914115</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0.0004015294834971428</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.83168445073744</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0.00236882921308279</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.83168445073744</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0.008296096697449684</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.83168445073744</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.005927535705268383</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.83168445073744</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,13 +31946,13 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0.002990839071571827</v>
       </c>
       <c r="JB39" t="n">
-        <v>1.83168445073744</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC39" t="n">
-        <v>-0.0002396808027515653</v>
+        <v>-0.0001335535717869643</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>2.763165669875081</v>
+        <v>1.539675436723744</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32741,13 +32741,13 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0.0004488253034651279</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.090689570091412</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC40" t="n">
-        <v>5.530602695210746</v>
+        <v>3.081730933809367</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.4143489953694587</v>
+        <v>0.2308811771930159</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33536,13 +33536,13 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0</v>
+        <v>-0.001253198832273483</v>
       </c>
       <c r="JB41" t="n">
-        <v>0.1496946894453832</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC41" t="n">
-        <v>3.592426513096849</v>
+        <v>2.001751440677884</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.5180711213966482</v>
+        <v>0.2886765953680197</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34331,13 +34331,13 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0</v>
+        <v>-0.002609313931316137</v>
       </c>
       <c r="JB42" t="n">
-        <v>0.1496946894453832</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC42" t="n">
-        <v>4.214285516657267</v>
+        <v>2.348260187964887</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.7426523329458294</v>
+        <v>0.4138166931146126</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35126,13 +35126,13 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.0002912012860178947</v>
       </c>
       <c r="JB43" t="n">
-        <v>0.8906895700914117</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC43" t="n">
-        <v>5.181811757220412</v>
+        <v>2.887379778388652</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.7944912398974422</v>
+        <v>0.4427015448511257</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.003331859596073627</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.63168445073744</v>
+        <v>-0.16</v>
       </c>
       <c r="JC44" t="n">
-        <v>6.028196949566889</v>
+        <v>3.358997725057585</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.8420005771651439</v>
+        <v>0.4691744069131162</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.005360431037843227</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.83168445073744</v>
+        <v>-0.16</v>
       </c>
       <c r="JC45" t="n">
-        <v>6.917766983143647</v>
+        <v>3.854679273798357</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.3799785344329387</v>
+        <v>0.2117296837708128</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0.005144746974110603</v>
       </c>
       <c r="JB46" t="n">
-        <v>1.090689570091412</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC46" t="n">
-        <v>6.835025108445538</v>
+        <v>3.808574208374842</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.1835122646265243</v>
+        <v>0.1022564029922444</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0</v>
+        <v>-0.004905082285404205</v>
       </c>
       <c r="JB47" t="n">
-        <v>0.1496946894453832</v>
+        <v>0.16</v>
       </c>
       <c r="JC47" t="n">
-        <v>6.821773102704443</v>
+        <v>3.801189972815334</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.08743813058663204</v>
+        <v>0.04872151876334413</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>-0.007741818204522133</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.5913001912006451</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC48" t="n">
-        <v>6.812991304446424</v>
+        <v>3.79629662831082</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.02590730817096692</v>
+        <v>0.01443562508945342</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>-0.01189721282571554</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.5913001912006451</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC49" t="n">
-        <v>6.777274151917468</v>
+        <v>3.77639381926476</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.01713671825815635</v>
+        <v>0.009546922343961529</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>-0.01122879236936569</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.5913001912006451</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC50" t="n">
-        <v>6.785626987913744</v>
+        <v>3.781046008672738</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.008768927782168255</v>
+        <v>0.00488328902341728</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>-0.01157604809850454</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.5913001912006451</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC51" t="n">
-        <v>6.786016749463758</v>
+        <v>3.781260968087588</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.004482699808797777</v>
+        <v>0.002495548749451251</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>-0.009327462874352932</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.5913001912006451</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC52" t="n">
-        <v>6.786209009218313</v>
+        <v>3.78136589139576</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.001682096480400876</v>
+        <v>0.000935051067141269</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>-0.007698029279708862</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.5913001912006451</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC53" t="n">
-        <v>6.785086852381644</v>
+        <v>3.780738300270838</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0009148816646433416</v>
+        <v>0.0005073287118775922</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>-0.006866039708256721</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.5913001912006451</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC54" t="n">
-        <v>6.785232822089654</v>
+        <v>3.780817451154166</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.000437664582460989</v>
+        <v>0.0002421610146236401</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>-0.00587456114590168</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.5913001912006451</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC55" t="n">
-        <v>6.785193483142717</v>
+        <v>3.780793294986589</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.0002695234777643763</v>
+        <v>0.0001475130432024312</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>-0.004331310279667377</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.5913001912006451</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC56" t="n">
-        <v>6.785293863419652</v>
+        <v>3.780847029037397</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.0001380823128904778</v>
+        <v>7.529079428386522e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>-0.005590627901256084</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.3496946894453832</v>
+        <v>0.16</v>
       </c>
       <c r="JC57" t="n">
-        <v>6.785301375062728</v>
+        <v>3.780849024444655</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>6.493651915496244e-05</v>
+        <v>3.396463210062193e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0.004008644260466099</v>
       </c>
       <c r="JB58" t="n">
-        <v>1.090689570091412</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC58" t="n">
-        <v>6.785292046198006</v>
+        <v>3.780841612648595</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>3.97701232216949e-05</v>
+        <v>1.930378117749152e-05</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.00176589097827673</v>
       </c>
       <c r="JB59" t="n">
-        <v>1.090689570091412</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC59" t="n">
-        <v>6.785306619137414</v>
+        <v>3.780847518348274</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>1.481539171982363e-05</v>
+        <v>6.65611277636684e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>-0.005623732227832079</v>
       </c>
       <c r="JB60" t="n">
-        <v>0.3496946894453833</v>
+        <v>0.16</v>
       </c>
       <c r="JC60" t="n">
-        <v>6.78529761655959</v>
+        <v>3.780840230756323</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>4.264322417369065e-06</v>
+        <v>1.468457874272584e-07</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>-0.008761273697018623</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.3913001912006451</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC61" t="n">
-        <v>6.785290149982596</v>
+        <v>3.78083386043577</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-5.494870763551826e-07</v>
+        <v>-2.77474353817759e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>-0.008792651817202568</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.5913001912006451</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC62" t="n">
-        <v>6.785285894804425</v>
+        <v>3.780829274526238</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>-3.062365791830193e-06</v>
+        <v>-4.031182895915095e-06</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>-0.007973892614245415</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.5913001912006451</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC63" t="n">
-        <v>6.785280172525395</v>
+        <v>3.780823841394769</v>
       </c>
     </row>
     <row r="64">
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>-0.004724967759102583</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.1496946894453832</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC64" t="n">
-        <v>6.785275103170026</v>
+        <v>3.780818794773702</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>-3.735991635587426e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0.002770441584289074</v>
       </c>
       <c r="JB65" t="n">
-        <v>1.090689570091412</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC65" t="n">
-        <v>6.785270738196057</v>
+        <v>3.780819113053918</v>
       </c>
     </row>
     <row r="66">
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0.01210055034607649</v>
       </c>
       <c r="JB66" t="n">
-        <v>1.83168445073744</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC66" t="n">
-        <v>6.785271829442515</v>
+        <v>3.780820204300375</v>
       </c>
     </row>
     <row r="67">
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0.002323332242667675</v>
       </c>
       <c r="JB67" t="n">
-        <v>1.090689570091412</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC67" t="n">
-        <v>6.785271139835378</v>
+        <v>3.780819514693239</v>
       </c>
     </row>
     <row r="68">
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>-0.01059615891426802</v>
       </c>
       <c r="JB68" t="n">
-        <v>0.3496946894453833</v>
+        <v>0.16</v>
       </c>
       <c r="JC68" t="n">
-        <v>6.78527117014778</v>
+        <v>3.780819545005641</v>
       </c>
     </row>
     <row r="69">
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>-0.01718518137931824</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.3913001912006451</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC69" t="n">
-        <v>6.78527098069527</v>
+        <v>3.780819355553131</v>
       </c>
     </row>
     <row r="70">
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>-0.01823918893933296</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.5913001912006451</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC70" t="n">
-        <v>6.785271033741973</v>
+        <v>3.780819408599834</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>-0.01821741834282875</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.5913001912006451</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC71" t="n">
-        <v>6.785271086788676</v>
+        <v>3.780819461646536</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>-0.01623236760497093</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.5913001912006451</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC72" t="n">
-        <v>6.785271048898173</v>
+        <v>3.780819423756034</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>-0.01306863781064749</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.5913001912006451</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC73" t="n">
-        <v>6.785270920070467</v>
+        <v>3.780819294928327</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>-0.0105469124391675</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.5913001912006451</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC74" t="n">
-        <v>6.785270776086559</v>
+        <v>3.78081915094442</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>-0.008791154250502586</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.5913001912006451</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC75" t="n">
-        <v>6.785270616946451</v>
+        <v>3.780818991804312</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>-0.007225861307233572</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.5913001912006451</v>
+        <v>0.16</v>
       </c>
       <c r="JC76" t="n">
-        <v>6.785270669993154</v>
+        <v>3.780819044851015</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>-0.007296106778085232</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.5913001912006451</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC77" t="n">
-        <v>6.785270616946451</v>
+        <v>3.780818991804312</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>-0.006199374329298735</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.5913001912006451</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC78" t="n">
-        <v>6.785270616946451</v>
+        <v>3.780818991804312</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>-0.003928804770112038</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.5913001912006451</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC79" t="n">
-        <v>6.785270435072042</v>
+        <v>3.780818809929903</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>-0.002265089191496372</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.5913001912006451</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC80" t="n">
-        <v>6.78527060179025</v>
+        <v>3.780818976648111</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>-0.003932519815862179</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.5913001912006451</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC81" t="n">
-        <v>6.785270798820861</v>
+        <v>3.780819173678721</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>-0.005596689414232969</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.5913001912006451</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC82" t="n">
-        <v>6.785270639680753</v>
+        <v>3.780819014538613</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>-0.003841330297291279</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.5913001912006451</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC83" t="n">
-        <v>6.785270677571254</v>
+        <v>3.780819052429115</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>-0.002136635594069958</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.5913001912006451</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC84" t="n">
-        <v>6.785270874601864</v>
+        <v>3.780819249459725</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>-0.004055601079016924</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.5913001912006451</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC85" t="n">
-        <v>6.785270851867563</v>
+        <v>3.780819226725424</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>-0.006169713102281094</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.5913001912006451</v>
+        <v>-0.16</v>
       </c>
       <c r="JC86" t="n">
-        <v>6.785270700305555</v>
+        <v>3.780819075163416</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>-0.006324717774987221</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.5913001912006451</v>
+        <v>-0.3</v>
       </c>
       <c r="JC87" t="n">
-        <v>6.785270624524552</v>
+        <v>3.780818999382412</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0</v>
+        <v>-0.005430737510323524</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.5913001912006451</v>
+        <v>-0.16</v>
       </c>
       <c r="JC88" t="n">
-        <v>6.785270723039857</v>
+        <v>3.780819097897718</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>-0.00298679992556572</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.5913001912006451</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC89" t="n">
-        <v>6.785270730617957</v>
+        <v>3.780819105475818</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>-0.00318244518712163</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.5913001912006451</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC90" t="n">
-        <v>6.785270995851471</v>
+        <v>3.780819370709332</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>-0.004651508294045925</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.5913001912006451</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC91" t="n">
-        <v>6.785270700305555</v>
+        <v>3.780819075163416</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>-0.00356008461676538</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.5913001912006451</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC92" t="n">
-        <v>6.785270942804768</v>
+        <v>3.780819317662628</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>-0.005309656262397766</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.5913001912006451</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC93" t="n">
-        <v>6.785271026163873</v>
+        <v>3.780819401021733</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>-0.001419235020875931</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.5913001912006451</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC94" t="n">
-        <v>6.785270859445664</v>
+        <v>3.780819234303525</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>-0.004008029121905565</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.5913001912006451</v>
+        <v>-0.3</v>
       </c>
       <c r="JC95" t="n">
-        <v>6.785271048898173</v>
+        <v>3.780819423756034</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>-0.007550916168838739</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.5913001912006451</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC96" t="n">
-        <v>6.785270700305555</v>
+        <v>3.780819075163416</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>-0.00996122695505619</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.5913001912006451</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC97" t="n">
-        <v>6.785270495696844</v>
+        <v>3.780818870554705</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>-0.00954118836671114</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.5913001912006451</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC98" t="n">
-        <v>6.78527060936835</v>
+        <v>3.780818984226211</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>-0.007645200937986374</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.5913001912006451</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC99" t="n">
-        <v>6.785270624524552</v>
+        <v>3.780818999382412</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>-0.006330849602818489</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.5913001912006451</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC100" t="n">
-        <v>6.78527038960344</v>
+        <v>3.7808187644613</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>-0.006241708062589169</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.5913001912006451</v>
+        <v>-0.3</v>
       </c>
       <c r="JC101" t="n">
-        <v>6.785270450228242</v>
+        <v>3.780818825086103</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>-0.0056228032335639</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.5913001912006451</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC102" t="n">
-        <v>6.785270321400535</v>
+        <v>3.780818696258396</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>-0.001151467673480511</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.5913001912006451</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC103" t="n">
-        <v>6.785270457806344</v>
+        <v>3.780818832664204</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>-0.001984583213925362</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.5913001912006451</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC104" t="n">
-        <v>6.785270632102652</v>
+        <v>3.780819006960512</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>-0.00363077549263835</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.5913001912006451</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC105" t="n">
-        <v>6.785270776086559</v>
+        <v>3.78081915094442</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>-0.00376955745741725</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.5913001912006451</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC106" t="n">
-        <v>6.78527060936835</v>
+        <v>3.780818984226211</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>-0.004464846104383469</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.5913001912006451</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC107" t="n">
-        <v>6.78527060179025</v>
+        <v>3.780818976648111</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>-0.005633807741105556</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.5913001912006451</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC108" t="n">
-        <v>6.785270313822435</v>
+        <v>3.780818688680296</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>-0.004885272588580847</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.5913001912006451</v>
+        <v>-0.16</v>
       </c>
       <c r="JC109" t="n">
-        <v>6.785270328978636</v>
+        <v>3.780818703836497</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>-0.004094642587006092</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.5913001912006451</v>
+        <v>-0.16</v>
       </c>
       <c r="JC110" t="n">
-        <v>6.785270556321648</v>
+        <v>3.780818931179509</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>-0.002369292080402374</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.5913001912006451</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC111" t="n">
-        <v>6.785270541165447</v>
+        <v>3.780818916023307</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>-0.003464308567345142</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.5913001912006451</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC112" t="n">
-        <v>6.785270647258852</v>
+        <v>3.780819022116713</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>-0.003999015316367149</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.5913001912006451</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC113" t="n">
-        <v>6.785270374447238</v>
+        <v>3.780818749305099</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>-0.003068495541810989</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.5913001912006451</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC114" t="n">
-        <v>6.785270472962543</v>
+        <v>3.780818847820404</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>-0.002476496621966362</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.5913001912006451</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC115" t="n">
-        <v>6.785270624524552</v>
+        <v>3.780818999382412</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>-0.002445979975163937</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.5913001912006451</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC116" t="n">
-        <v>6.785270639680753</v>
+        <v>3.780819014538613</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>-0.002267452888190746</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.5913001912006451</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC117" t="n">
-        <v>6.785270616946451</v>
+        <v>3.780818991804312</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>-0.001776630990207195</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.5913001912006451</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC118" t="n">
-        <v>6.785270700305555</v>
+        <v>3.780819075163416</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>-0.002990321721881628</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.5913001912006451</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC119" t="n">
-        <v>6.785270798820861</v>
+        <v>3.780819173678721</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>-0.004019010812044144</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.5913001912006451</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC120" t="n">
-        <v>6.785270632102652</v>
+        <v>3.780819006960512</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>-0.00391075387597084</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.5913001912006451</v>
+        <v>-0.16</v>
       </c>
       <c r="JC121" t="n">
-        <v>6.785270616946451</v>
+        <v>3.780818991804312</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>-0.003508384339511395</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.5913001912006451</v>
+        <v>-0.3</v>
       </c>
       <c r="JC122" t="n">
-        <v>6.785270586634049</v>
+        <v>3.78081896149191</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>-0.00306773092597723</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.5913001912006451</v>
+        <v>-0.16</v>
       </c>
       <c r="JC123" t="n">
-        <v>6.785270571477849</v>
+        <v>3.78081894633571</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>-0.003230109112337232</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.5913001912006451</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC124" t="n">
-        <v>6.78527060936835</v>
+        <v>3.780818984226211</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>-0.002750666812062263</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.5913001912006451</v>
+        <v>0.1900000000000003</v>
       </c>
       <c r="JC125" t="n">
-        <v>6.785270624524552</v>
+        <v>3.780818999382412</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>-0.001994465477764606</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.5913001912006451</v>
+        <v>1</v>
       </c>
       <c r="JC126" t="n">
-        <v>6.785270616946451</v>
+        <v>3.780818991804312</v>
       </c>
     </row>
   </sheetData>
